--- a/sample/2026년_금융정보단말기 업로드 sample.xlsx
+++ b/sample/2026년_금융정보단말기 업로드 sample.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2554" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2518" uniqueCount="276">
   <si>
     <t>2026 전산업무비 ID</t>
   </si>
@@ -137,9 +137,6 @@
     <t>김계환</t>
   </si>
   <si>
-    <t>COST-2026-1739</t>
-  </si>
-  <si>
     <t>발행시장실</t>
   </si>
   <si>
@@ -158,18 +155,12 @@
     <t>USD</t>
   </si>
   <si>
-    <t>COST-2026-1740</t>
-  </si>
-  <si>
     <t>백승윤</t>
   </si>
   <si>
     <t>Open Bloomberg</t>
   </si>
   <si>
-    <t>COST-2026-1738</t>
-  </si>
-  <si>
     <t>발행시장실장</t>
   </si>
   <si>
@@ -197,9 +188,6 @@
     <t>주현선</t>
   </si>
   <si>
-    <t>COST-2026-1735</t>
-  </si>
-  <si>
     <t>미래전략개발부</t>
   </si>
   <si>
@@ -215,12 +203,6 @@
     <t>EIKON, Datastream</t>
   </si>
   <si>
-    <t>COST-2026-1734</t>
-  </si>
-  <si>
-    <t>COST-2026-1736</t>
-  </si>
-  <si>
     <t>코스콤</t>
   </si>
   <si>
@@ -266,9 +248,6 @@
     <t>월별</t>
   </si>
   <si>
-    <t>COST-2026-1810</t>
-  </si>
-  <si>
     <t>자금운용실</t>
   </si>
   <si>
@@ -306,9 +285,6 @@
   </si>
   <si>
     <t>별도품의(신규)</t>
-  </si>
-  <si>
-    <t>COST-2026-1809</t>
   </si>
   <si>
     <t>유가증권운용전략팀</t>
@@ -531,9 +507,6 @@
     <t>레피니티브 론커넥터 구독</t>
   </si>
   <si>
-    <t>COST-2026-1729</t>
-  </si>
-  <si>
     <t>리스크관리부</t>
   </si>
   <si>
@@ -549,15 +522,9 @@
     <t>단말기</t>
   </si>
   <si>
-    <t>COST-2026-1727</t>
-  </si>
-  <si>
     <t>EIKON</t>
   </si>
   <si>
-    <t>COST-2026-1725</t>
-  </si>
-  <si>
     <t>장석건</t>
   </si>
   <si>
@@ -574,9 +541,6 @@
   </si>
   <si>
     <t>RDM(리스크 데이터마켓) 연계 - 제외</t>
-  </si>
-  <si>
-    <t>COST-2026-1730</t>
   </si>
   <si>
     <t>S&amp;P</t>
@@ -1647,33 +1611,31 @@
       <c r="T6" s="4"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="K7" s="5">
         <v>2596</v>
@@ -1705,33 +1667,31 @@
       <c r="T7" s="4"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>48</v>
-      </c>
+      <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K8" s="6">
         <v>2439.03</v>
@@ -1763,18 +1723,16 @@
       <c r="T8" s="4"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>23</v>
@@ -1786,7 +1744,7 @@
         <v>25</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>27</v>
@@ -1801,7 +1759,7 @@
         <v>6481200</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O9" s="7">
         <v>1</v>
@@ -1821,18 +1779,16 @@
       <c r="T9" s="4"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>23</v>
@@ -1844,7 +1800,7 @@
         <v>25</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>27</v>
@@ -1859,10 +1815,10 @@
         <v>6481200</v>
       </c>
       <c r="N10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="O10" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="P10" s="5">
         <v>0</v>
@@ -1879,18 +1835,16 @@
       <c r="T10" s="4"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>23</v>
@@ -1902,7 +1856,7 @@
         <v>25</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>27</v>
@@ -1917,10 +1871,10 @@
         <v>6481200</v>
       </c>
       <c r="N11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="O11" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="P11" s="5">
         <v>0</v>
@@ -1937,30 +1891,28 @@
       <c r="T11" s="4"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>61</v>
-      </c>
+      <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>27</v>
@@ -1995,18 +1947,16 @@
       <c r="T12" s="4"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>67</v>
-      </c>
+      <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>33</v>
@@ -2018,10 +1968,10 @@
         <v>25</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K13" s="6">
         <v>2542</v>
@@ -2053,18 +2003,16 @@
       <c r="T13" s="4"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>68</v>
-      </c>
+      <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>23</v>
@@ -2076,7 +2024,7 @@
         <v>25</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>27</v>
@@ -2091,10 +2039,10 @@
         <v>7669200</v>
       </c>
       <c r="N14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O14" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="P14" s="6">
         <v>0</v>
@@ -2114,13 +2062,13 @@
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>23</v>
@@ -2129,7 +2077,7 @@
         <v>24</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>38</v>
@@ -2170,13 +2118,13 @@
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>23</v>
@@ -2185,7 +2133,7 @@
         <v>24</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>38</v>
@@ -2226,28 +2174,28 @@
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K17" s="6">
         <v>2477</v>
@@ -2282,13 +2230,13 @@
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>33</v>
@@ -2303,7 +2251,7 @@
         <v>34</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K18" s="5">
         <v>2561</v>
@@ -2338,13 +2286,13 @@
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>33</v>
@@ -2356,10 +2304,10 @@
         <v>25</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K19" s="6">
         <v>2437</v>
@@ -2371,10 +2319,10 @@
         <v>42593301.120000005</v>
       </c>
       <c r="N19" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="O19" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O19" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="P19" s="5">
         <v>2437</v>
@@ -2386,23 +2334,21 @@
         <v>42593301.120000005</v>
       </c>
       <c r="S19" s="6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="T19" s="4"/>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>84</v>
-      </c>
+      <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>23</v>
@@ -2411,7 +2357,7 @@
         <v>24</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>38</v>
@@ -2449,18 +2395,16 @@
       <c r="T20" s="4"/>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>84</v>
-      </c>
+      <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>23</v>
@@ -2469,7 +2413,7 @@
         <v>24</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>38</v>
@@ -2505,22 +2449,20 @@
         <v>29</v>
       </c>
       <c r="T21" s="4" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>84</v>
-      </c>
+      <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>23</v>
@@ -2529,7 +2471,7 @@
         <v>24</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>38</v>
@@ -2567,18 +2509,16 @@
       <c r="T22" s="4"/>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>84</v>
-      </c>
+      <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>92</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>23</v>
@@ -2587,7 +2527,7 @@
         <v>24</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>38</v>
@@ -2623,22 +2563,20 @@
         <v>29</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>84</v>
-      </c>
+      <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>23</v>
@@ -2647,7 +2585,7 @@
         <v>24</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>38</v>
@@ -2685,18 +2623,16 @@
       <c r="T24" s="4"/>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>84</v>
-      </c>
+      <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>23</v>
@@ -2705,7 +2641,7 @@
         <v>24</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>38</v>
@@ -2723,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="P25" s="5">
         <v>0</v>
@@ -2741,22 +2677,20 @@
         <v>29</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>33</v>
@@ -2765,13 +2699,13 @@
         <v>24</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K26" s="6">
         <v>2490.1500000000005</v>
@@ -2803,18 +2737,16 @@
       <c r="T26" s="4"/>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>33</v>
@@ -2823,13 +2755,13 @@
         <v>24</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K27" s="6">
         <v>2477</v>
@@ -2861,18 +2793,16 @@
       <c r="T27" s="4"/>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>33</v>
@@ -2881,13 +2811,13 @@
         <v>24</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K28" s="6">
         <v>2477</v>
@@ -2919,18 +2849,16 @@
       <c r="T28" s="4"/>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>33</v>
@@ -2939,13 +2867,13 @@
         <v>24</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K29" s="6">
         <v>2477</v>
@@ -2977,18 +2905,16 @@
       <c r="T29" s="4"/>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>33</v>
@@ -2997,13 +2923,13 @@
         <v>24</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K30" s="6">
         <v>2477</v>
@@ -3035,18 +2961,16 @@
       <c r="T30" s="4"/>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>33</v>
@@ -3055,13 +2979,13 @@
         <v>24</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K31" s="6">
         <v>2477</v>
@@ -3093,18 +3017,16 @@
       <c r="T31" s="4"/>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>33</v>
@@ -3113,13 +3035,13 @@
         <v>24</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K32" s="6">
         <v>2477</v>
@@ -3151,18 +3073,16 @@
       <c r="T32" s="4"/>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>33</v>
@@ -3171,13 +3091,13 @@
         <v>24</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K33" s="6">
         <v>2477</v>
@@ -3209,18 +3129,16 @@
       <c r="T33" s="4"/>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>33</v>
@@ -3229,13 +3147,13 @@
         <v>24</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K34" s="6">
         <v>2477</v>
@@ -3267,18 +3185,16 @@
       <c r="T34" s="4"/>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>33</v>
@@ -3287,13 +3203,13 @@
         <v>24</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K35" s="6">
         <v>2477</v>
@@ -3325,18 +3241,16 @@
       <c r="T35" s="4"/>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>33</v>
@@ -3345,13 +3259,13 @@
         <v>24</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K36" s="6">
         <v>2477</v>
@@ -3383,18 +3297,16 @@
       <c r="T36" s="4"/>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>33</v>
@@ -3403,13 +3315,13 @@
         <v>24</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K37" s="6">
         <v>12261.798083333335</v>
@@ -3441,18 +3353,16 @@
       <c r="T37" s="4"/>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>33</v>
@@ -3461,13 +3371,13 @@
         <v>24</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K38" s="6">
         <v>5041.674000000001</v>
@@ -3494,23 +3404,21 @@
         <v>93724488</v>
       </c>
       <c r="S38" s="6" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="T38" s="4"/>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>33</v>
@@ -3519,13 +3427,13 @@
         <v>24</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K39" s="6">
         <v>798.1050000000001</v>
@@ -3560,13 +3468,13 @@
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="4" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>33</v>
@@ -3581,7 +3489,7 @@
         <v>34</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K40" s="5">
         <v>2574.45</v>
@@ -3616,13 +3524,13 @@
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="4" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>33</v>
@@ -3637,7 +3545,7 @@
         <v>34</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K41" s="6">
         <v>2430.41</v>
@@ -3672,13 +3580,13 @@
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>23</v>
@@ -3690,7 +3598,7 @@
         <v>25</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>27</v>
@@ -3705,10 +3613,10 @@
         <v>6481200</v>
       </c>
       <c r="N42" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O42" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O42" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="P42" s="5">
         <v>0</v>
@@ -3728,13 +3636,13 @@
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>23</v>
@@ -3746,7 +3654,7 @@
         <v>25</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>27</v>
@@ -3761,10 +3669,10 @@
         <v>6745200</v>
       </c>
       <c r="N43" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O43" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O43" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="P43" s="5">
         <v>0</v>
@@ -3784,16 +3692,16 @@
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>24</v>
@@ -3802,7 +3710,7 @@
         <v>25</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>27</v>
@@ -3840,28 +3748,28 @@
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K45" s="6">
         <v>2711.5</v>
@@ -3896,28 +3804,28 @@
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K46" s="6">
         <v>308</v>
@@ -3944,7 +3852,7 @@
         <v>5921465.0879999995</v>
       </c>
       <c r="S46" s="6" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="T46" s="4"/>
     </row>
@@ -3952,25 +3860,25 @@
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>27</v>
@@ -4008,28 +3916,28 @@
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K48" s="6">
         <v>2711.5</v>
@@ -4064,28 +3972,28 @@
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K49" s="6">
         <v>308</v>
@@ -4112,7 +4020,7 @@
         <v>5921465.0879999995</v>
       </c>
       <c r="S49" s="6" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="T49" s="4"/>
     </row>
@@ -4120,25 +4028,25 @@
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>27</v>
@@ -4176,25 +4084,25 @@
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>27</v>
@@ -4232,13 +4140,13 @@
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>33</v>
@@ -4250,10 +4158,10 @@
         <v>25</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K52" s="6">
         <v>2436.5</v>
@@ -4288,28 +4196,28 @@
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K53" s="6">
         <v>2.53</v>
@@ -4321,10 +4229,10 @@
         <v>44218.7328</v>
       </c>
       <c r="N53" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O53" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O53" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="P53" s="5">
         <v>2.53</v>
@@ -4344,13 +4252,13 @@
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>33</v>
@@ -4362,10 +4270,10 @@
         <v>25</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K54" s="6">
         <v>2436.5</v>
@@ -4400,13 +4308,13 @@
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>33</v>
@@ -4415,13 +4323,13 @@
         <v>24</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K55" s="6">
         <v>2436.5</v>
@@ -4456,13 +4364,13 @@
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>33</v>
@@ -4471,13 +4379,13 @@
         <v>24</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K56" s="6">
         <v>2436.5</v>
@@ -4512,28 +4420,28 @@
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="K57" s="6">
         <v>92.65</v>
@@ -4568,22 +4476,22 @@
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K58" s="6">
         <v>149.33</v>
@@ -4618,22 +4526,22 @@
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K59" s="6">
         <v>102.46</v>
@@ -4668,22 +4576,22 @@
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K60" s="6">
         <v>141.81</v>
@@ -4718,19 +4626,19 @@
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>27</v>
@@ -4768,28 +4676,28 @@
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K62" s="5">
         <v>2436.5</v>
@@ -4824,22 +4732,22 @@
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K63" s="6">
         <v>38.5</v>
@@ -4851,10 +4759,10 @@
         <v>672893.76</v>
       </c>
       <c r="N63" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="O63" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O63" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="P63" s="5">
         <v>38.5</v>
@@ -4874,22 +4782,22 @@
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K64" s="6">
         <v>17.49</v>
@@ -4901,10 +4809,10 @@
         <v>305686.02239999996</v>
       </c>
       <c r="N64" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O64" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O64" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="P64" s="5">
         <v>17.49</v>
@@ -4924,22 +4832,22 @@
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K65" s="6">
         <v>2.53</v>
@@ -4951,10 +4859,10 @@
         <v>44218.7328</v>
       </c>
       <c r="N65" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O65" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O65" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="P65" s="5">
         <v>2.53</v>
@@ -4974,28 +4882,28 @@
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K66" s="6">
         <v>2750</v>
@@ -5007,10 +4915,10 @@
         <v>48063840</v>
       </c>
       <c r="N66" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O66" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O66" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="P66" s="5">
         <v>2750</v>
@@ -5022,7 +4930,7 @@
         <v>48063840</v>
       </c>
       <c r="S66" s="6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="T66" s="9"/>
     </row>
@@ -5030,28 +4938,28 @@
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="K67" s="6">
         <v>449.53</v>
@@ -5063,10 +4971,10 @@
         <v>9219392.788799997</v>
       </c>
       <c r="N67" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="O67" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O67" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="P67" s="5">
         <v>449.53</v>
@@ -5086,22 +4994,22 @@
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="K68" s="6">
         <v>1714.86</v>
@@ -5113,10 +5021,10 @@
         <v>35169995.1456</v>
       </c>
       <c r="N68" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O68" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O68" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="P68" s="5">
         <v>1714.86</v>
@@ -5134,13 +5042,13 @@
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="10" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>33</v>
@@ -5152,10 +5060,10 @@
         <v>25</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K69" s="5">
         <v>2436.5</v>
@@ -5190,25 +5098,25 @@
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="10" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H70" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="J70" s="4" t="s">
         <v>27</v>
@@ -5238,23 +5146,21 @@
         <v>23870893</v>
       </c>
       <c r="S70" s="6" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="T70" s="10"/>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
-        <v>172</v>
-      </c>
+      <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="4" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>23</v>
@@ -5263,16 +5169,16 @@
         <v>24</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="J71" s="4" t="s">
         <v>27</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="L71" s="6">
         <v>397100.00000000006</v>
@@ -5281,10 +5187,10 @@
         <v>4765200.000000001</v>
       </c>
       <c r="N71" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="O71" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O71" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="P71" s="5">
         <v>0</v>
@@ -5301,36 +5207,34 @@
       <c r="T71" s="4"/>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
-        <v>178</v>
-      </c>
+      <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="4" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="J72" s="4" t="s">
         <v>27</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="L72" s="6">
         <v>2972970.0000000005</v>
@@ -5359,33 +5263,31 @@
       <c r="T72" s="10"/>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
-        <v>180</v>
-      </c>
+      <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="4" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K73" s="6">
         <v>2436.5</v>
@@ -5412,38 +5314,36 @@
         <v>44443030.72</v>
       </c>
       <c r="S73" s="6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="T73" s="10"/>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
-        <v>180</v>
-      </c>
+      <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="4" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K74" s="6">
         <v>9020.96</v>
@@ -5455,10 +5355,10 @@
         <v>157666173.8496</v>
       </c>
       <c r="N74" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O74" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O74" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="P74" s="5">
         <v>9020.96</v>
@@ -5468,40 +5368,38 @@
       </c>
       <c r="R74" s="5"/>
       <c r="S74" s="6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="T74" s="4" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
-        <v>187</v>
-      </c>
+      <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G75" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>184</v>
-      </c>
       <c r="H75" s="4" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K75" s="6">
         <v>13206.4166</v>
@@ -5513,10 +5411,10 @@
         <v>230818579.79481602</v>
       </c>
       <c r="N75" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O75" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O75" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="P75" s="5">
         <v>13206.4166</v>
@@ -5526,25 +5424,23 @@
       </c>
       <c r="R75" s="5"/>
       <c r="S75" s="6" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="T75" s="4" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
-        <v>172</v>
-      </c>
+      <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="4" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>23</v>
@@ -5553,10 +5449,10 @@
         <v>24</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="J76" s="4" t="s">
         <v>27</v>
@@ -5571,10 +5467,10 @@
         <v>4765200</v>
       </c>
       <c r="N76" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O76" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O76" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="P76" s="5">
         <v>0</v>
@@ -5591,18 +5487,16 @@
       <c r="T76" s="4"/>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
-        <v>172</v>
-      </c>
+      <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="4" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>23</v>
@@ -5611,10 +5505,10 @@
         <v>24</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="J77" s="4" t="s">
         <v>27</v>
@@ -5629,10 +5523,10 @@
         <v>3036000</v>
       </c>
       <c r="N77" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="O77" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O77" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="P77" s="5">
         <v>0</v>
@@ -5649,18 +5543,16 @@
       <c r="T77" s="4"/>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
-        <v>172</v>
-      </c>
+      <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="4" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>23</v>
@@ -5669,10 +5561,10 @@
         <v>24</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>27</v>
@@ -5710,28 +5602,28 @@
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G79" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K79" s="6">
         <v>141.81</v>
@@ -5766,28 +5658,28 @@
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G80" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K80" s="6">
         <v>141.81</v>
@@ -5822,28 +5714,28 @@
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G81" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K81" s="6">
         <v>141.81</v>
@@ -5878,28 +5770,28 @@
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G82" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K82" s="6">
         <v>141.81</v>
@@ -5934,28 +5826,28 @@
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G83" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K83" s="6">
         <v>141.81</v>
@@ -5990,28 +5882,28 @@
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G84" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K84" s="6">
         <v>141.81</v>
@@ -6046,28 +5938,28 @@
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G85" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K85" s="6">
         <v>141.81</v>
@@ -6102,28 +5994,28 @@
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G86" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K86" s="6">
         <v>141.81</v>
@@ -6158,28 +6050,28 @@
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G87" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K87" s="6">
         <v>141.81</v>
@@ -6214,28 +6106,28 @@
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G88" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K88" s="6">
         <v>7.5</v>
@@ -6270,28 +6162,28 @@
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E89" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="D89" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="E89" s="4" t="s">
-        <v>211</v>
-      </c>
       <c r="F89" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G89" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K89" s="6">
         <v>7.5</v>
@@ -6326,28 +6218,28 @@
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D90" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E90" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="E90" s="4" t="s">
-        <v>212</v>
-      </c>
       <c r="F90" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G90" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K90" s="6">
         <v>7.5</v>
@@ -6382,16 +6274,16 @@
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G91" s="4" t="s">
         <v>24</v>
@@ -6400,7 +6292,7 @@
         <v>25</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J91" s="4" t="s">
         <v>27</v>
@@ -6438,16 +6330,16 @@
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G92" s="4" t="s">
         <v>24</v>
@@ -6456,7 +6348,7 @@
         <v>25</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J92" s="4" t="s">
         <v>27</v>
@@ -6494,16 +6386,16 @@
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G93" s="4" t="s">
         <v>24</v>
@@ -6512,7 +6404,7 @@
         <v>25</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J93" s="4" t="s">
         <v>27</v>
@@ -6550,16 +6442,16 @@
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G94" s="4" t="s">
         <v>24</v>
@@ -6568,7 +6460,7 @@
         <v>25</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J94" s="4" t="s">
         <v>27</v>
@@ -6606,16 +6498,16 @@
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G95" s="4" t="s">
         <v>24</v>
@@ -6624,7 +6516,7 @@
         <v>25</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J95" s="4" t="s">
         <v>27</v>
@@ -6662,16 +6554,16 @@
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G96" s="4" t="s">
         <v>24</v>
@@ -6680,7 +6572,7 @@
         <v>25</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J96" s="4" t="s">
         <v>27</v>
@@ -6718,16 +6610,16 @@
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G97" s="4" t="s">
         <v>24</v>
@@ -6736,7 +6628,7 @@
         <v>25</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J97" s="4" t="s">
         <v>27</v>
@@ -6774,16 +6666,16 @@
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G98" s="4" t="s">
         <v>24</v>
@@ -6792,7 +6684,7 @@
         <v>25</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J98" s="4" t="s">
         <v>27</v>
@@ -6830,16 +6722,16 @@
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G99" s="4" t="s">
         <v>24</v>
@@ -6848,7 +6740,7 @@
         <v>25</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J99" s="4" t="s">
         <v>27</v>
@@ -6886,16 +6778,16 @@
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G100" s="4" t="s">
         <v>24</v>
@@ -6904,7 +6796,7 @@
         <v>25</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J100" s="4" t="s">
         <v>27</v>
@@ -6942,16 +6834,16 @@
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G101" s="4" t="s">
         <v>24</v>
@@ -6960,7 +6852,7 @@
         <v>25</v>
       </c>
       <c r="I101" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J101" s="4" t="s">
         <v>27</v>
@@ -6998,16 +6890,16 @@
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G102" s="4" t="s">
         <v>24</v>
@@ -7016,7 +6908,7 @@
         <v>25</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J102" s="4" t="s">
         <v>27</v>
@@ -7054,16 +6946,16 @@
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>24</v>
@@ -7072,7 +6964,7 @@
         <v>25</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J103" s="4" t="s">
         <v>27</v>
@@ -7110,16 +7002,16 @@
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G104" s="4" t="s">
         <v>24</v>
@@ -7128,7 +7020,7 @@
         <v>25</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J104" s="4" t="s">
         <v>27</v>
@@ -7166,16 +7058,16 @@
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G105" s="4" t="s">
         <v>24</v>
@@ -7184,7 +7076,7 @@
         <v>25</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J105" s="4" t="s">
         <v>27</v>
@@ -7222,16 +7114,16 @@
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G106" s="4" t="s">
         <v>24</v>
@@ -7240,7 +7132,7 @@
         <v>25</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J106" s="4" t="s">
         <v>27</v>
@@ -7278,16 +7170,16 @@
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G107" s="4" t="s">
         <v>24</v>
@@ -7296,7 +7188,7 @@
         <v>25</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J107" s="4" t="s">
         <v>27</v>
@@ -7334,16 +7226,16 @@
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E108" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="D108" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="E108" s="4" t="s">
-        <v>211</v>
-      </c>
       <c r="F108" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G108" s="4" t="s">
         <v>24</v>
@@ -7352,7 +7244,7 @@
         <v>25</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J108" s="4" t="s">
         <v>27</v>
@@ -7390,16 +7282,16 @@
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D109" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E109" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="E109" s="4" t="s">
-        <v>212</v>
-      </c>
       <c r="F109" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G109" s="4" t="s">
         <v>24</v>
@@ -7408,7 +7300,7 @@
         <v>25</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J109" s="4" t="s">
         <v>27</v>
@@ -7446,16 +7338,16 @@
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G110" s="4" t="s">
         <v>24</v>
@@ -7464,7 +7356,7 @@
         <v>25</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J110" s="4" t="s">
         <v>27</v>
@@ -7502,16 +7394,16 @@
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G111" s="4" t="s">
         <v>24</v>
@@ -7520,7 +7412,7 @@
         <v>25</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J111" s="4" t="s">
         <v>27</v>
@@ -7558,16 +7450,16 @@
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G112" s="4" t="s">
         <v>24</v>
@@ -7576,7 +7468,7 @@
         <v>25</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J112" s="4" t="s">
         <v>27</v>
@@ -7614,16 +7506,16 @@
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G113" s="4" t="s">
         <v>24</v>
@@ -7632,7 +7524,7 @@
         <v>25</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J113" s="4" t="s">
         <v>27</v>
@@ -7670,16 +7562,16 @@
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G114" s="4" t="s">
         <v>24</v>
@@ -7688,7 +7580,7 @@
         <v>25</v>
       </c>
       <c r="I114" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J114" s="4" t="s">
         <v>27</v>
@@ -7726,16 +7618,16 @@
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G115" s="4" t="s">
         <v>24</v>
@@ -7744,7 +7636,7 @@
         <v>25</v>
       </c>
       <c r="I115" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J115" s="4" t="s">
         <v>27</v>
@@ -7782,16 +7674,16 @@
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G116" s="4" t="s">
         <v>24</v>
@@ -7800,7 +7692,7 @@
         <v>25</v>
       </c>
       <c r="I116" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J116" s="4" t="s">
         <v>27</v>
@@ -7838,16 +7730,16 @@
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G117" s="4" t="s">
         <v>24</v>
@@ -7856,7 +7748,7 @@
         <v>25</v>
       </c>
       <c r="I117" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J117" s="4" t="s">
         <v>27</v>
@@ -7894,16 +7786,16 @@
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G118" s="4" t="s">
         <v>24</v>
@@ -7912,7 +7804,7 @@
         <v>25</v>
       </c>
       <c r="I118" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J118" s="4" t="s">
         <v>27</v>
@@ -7950,16 +7842,16 @@
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G119" s="4" t="s">
         <v>24</v>
@@ -7968,7 +7860,7 @@
         <v>25</v>
       </c>
       <c r="I119" s="4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J119" s="4" t="s">
         <v>27</v>
@@ -8006,28 +7898,28 @@
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G120" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I120" s="4" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K120" s="6">
         <v>57.77</v>
@@ -8062,28 +7954,28 @@
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D121" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E121" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="E121" s="4" t="s">
-        <v>212</v>
-      </c>
       <c r="F121" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G121" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I121" s="4" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K121" s="6">
         <v>57.77</v>
@@ -8118,28 +8010,28 @@
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D122" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E122" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="E122" s="4" t="s">
-        <v>212</v>
-      </c>
       <c r="F122" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G122" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I122" s="4" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="J122" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K122" s="6">
         <v>35.97</v>
@@ -8174,28 +8066,28 @@
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G123" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I123" s="4" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="J123" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K123" s="6">
         <v>27.25</v>
@@ -8230,28 +8122,28 @@
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G124" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I124" s="4" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="J124" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K124" s="6">
         <v>27.25</v>
@@ -8286,28 +8178,28 @@
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G125" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I125" s="4" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K125" s="6">
         <v>141.81</v>
@@ -8342,13 +8234,13 @@
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>33</v>
@@ -8360,10 +8252,10 @@
         <v>25</v>
       </c>
       <c r="I126" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J126" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K126" s="5">
         <v>2596</v>
@@ -8375,7 +8267,7 @@
         <v>45372264.96</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O126" s="7">
         <v>1</v>
@@ -8398,13 +8290,13 @@
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>33</v>
@@ -8416,10 +8308,10 @@
         <v>25</v>
       </c>
       <c r="I127" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J127" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K127" s="5">
         <v>2596</v>
@@ -8431,7 +8323,7 @@
         <v>45372264.96</v>
       </c>
       <c r="N127" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O127" s="7">
         <v>1</v>
@@ -8454,13 +8346,13 @@
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>33</v>
@@ -8469,13 +8361,13 @@
         <v>24</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="I128" s="4" t="s">
         <v>34</v>
       </c>
       <c r="J128" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K128" s="5">
         <v>1249.6</v>
@@ -8510,13 +8402,13 @@
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>33</v>
@@ -8528,10 +8420,10 @@
         <v>25</v>
       </c>
       <c r="I129" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J129" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K129" s="5">
         <v>2596</v>
@@ -8543,7 +8435,7 @@
         <v>45372264.96</v>
       </c>
       <c r="N129" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O129" s="7">
         <v>1</v>
@@ -8566,13 +8458,13 @@
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="F130" s="4" t="s">
         <v>33</v>
@@ -8584,10 +8476,10 @@
         <v>25</v>
       </c>
       <c r="I130" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J130" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K130" s="5">
         <v>2436.5</v>
@@ -8622,13 +8514,13 @@
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="F131" s="4" t="s">
         <v>33</v>
@@ -8640,10 +8532,10 @@
         <v>25</v>
       </c>
       <c r="I131" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J131" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K131" s="5">
         <v>2436.5</v>
@@ -8678,13 +8570,13 @@
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="F132" s="4" t="s">
         <v>33</v>
@@ -8696,10 +8588,10 @@
         <v>25</v>
       </c>
       <c r="I132" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J132" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K132" s="5">
         <v>2436.5</v>
@@ -8734,13 +8626,13 @@
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="F133" s="4" t="s">
         <v>33</v>
@@ -8752,10 +8644,10 @@
         <v>25</v>
       </c>
       <c r="I133" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J133" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K133" s="5">
         <v>2436.5</v>
@@ -8790,13 +8682,13 @@
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>33</v>
@@ -8808,10 +8700,10 @@
         <v>25</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K134" s="5">
         <v>2436.5</v>
@@ -8846,13 +8738,13 @@
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F135" s="4" t="s">
         <v>33</v>
@@ -8864,10 +8756,10 @@
         <v>25</v>
       </c>
       <c r="I135" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J135" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K135" s="5">
         <v>2596</v>
@@ -8879,7 +8771,7 @@
         <v>45372264.96</v>
       </c>
       <c r="N135" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O135" s="7">
         <v>1</v>
@@ -8902,13 +8794,13 @@
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>33</v>
@@ -8920,10 +8812,10 @@
         <v>25</v>
       </c>
       <c r="I136" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J136" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K136" s="5">
         <v>2596</v>
@@ -8935,7 +8827,7 @@
         <v>45372264.96</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O136" s="7">
         <v>1</v>
@@ -8958,13 +8850,13 @@
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>33</v>
@@ -8976,10 +8868,10 @@
         <v>25</v>
       </c>
       <c r="I137" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J137" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K137" s="5">
         <v>2596</v>
@@ -8991,7 +8883,7 @@
         <v>45372264.96</v>
       </c>
       <c r="N137" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O137" s="7">
         <v>1</v>
@@ -9014,13 +8906,13 @@
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>33</v>
@@ -9032,10 +8924,10 @@
         <v>25</v>
       </c>
       <c r="I138" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J138" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K138" s="5">
         <v>2596</v>
@@ -9047,7 +8939,7 @@
         <v>45372264.96</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O138" s="7">
         <v>1</v>
@@ -9070,13 +8962,13 @@
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F139" s="4" t="s">
         <v>33</v>
@@ -9088,10 +8980,10 @@
         <v>25</v>
       </c>
       <c r="I139" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J139" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K139" s="5">
         <v>2436.5</v>
@@ -9126,13 +9018,13 @@
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>33</v>
@@ -9144,10 +9036,10 @@
         <v>25</v>
       </c>
       <c r="I140" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J140" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K140" s="5">
         <v>2436.5</v>
@@ -9182,13 +9074,13 @@
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="F141" s="4" t="s">
         <v>33</v>
@@ -9200,10 +9092,10 @@
         <v>25</v>
       </c>
       <c r="I141" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J141" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K141" s="5">
         <v>2596</v>
@@ -9215,7 +9107,7 @@
         <v>45372264.96</v>
       </c>
       <c r="N141" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O141" s="7">
         <v>1</v>
@@ -9238,13 +9130,13 @@
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>23</v>
@@ -9256,7 +9148,7 @@
         <v>25</v>
       </c>
       <c r="I142" s="4" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="J142" s="4" t="s">
         <v>27</v>
@@ -9271,7 +9163,7 @@
         <v>1584000</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O142" s="7">
         <v>1</v>
@@ -9294,13 +9186,13 @@
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F143" s="4" t="s">
         <v>23</v>
@@ -9312,7 +9204,7 @@
         <v>25</v>
       </c>
       <c r="I143" s="4" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="J143" s="4" t="s">
         <v>27</v>
@@ -9327,7 +9219,7 @@
         <v>4923600</v>
       </c>
       <c r="N143" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O143" s="7">
         <v>1</v>
@@ -9350,13 +9242,13 @@
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>23</v>
@@ -9368,7 +9260,7 @@
         <v>25</v>
       </c>
       <c r="I144" s="4" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="J144" s="4" t="s">
         <v>27</v>
@@ -9383,7 +9275,7 @@
         <v>1980000</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O144" s="7">
         <v>1</v>
@@ -9406,13 +9298,13 @@
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="F145" s="4" t="s">
         <v>23</v>
@@ -9424,7 +9316,7 @@
         <v>25</v>
       </c>
       <c r="I145" s="4" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="J145" s="4" t="s">
         <v>27</v>
@@ -9439,7 +9331,7 @@
         <v>1980000</v>
       </c>
       <c r="N145" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O145" s="7">
         <v>1</v>
@@ -9462,13 +9354,13 @@
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="F146" s="4" t="s">
         <v>23</v>
@@ -9480,7 +9372,7 @@
         <v>25</v>
       </c>
       <c r="I146" s="4" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="J146" s="4" t="s">
         <v>27</v>
@@ -9495,7 +9387,7 @@
         <v>1980000</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O146" s="7">
         <v>1</v>
@@ -9518,13 +9410,13 @@
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="F147" s="4" t="s">
         <v>23</v>
@@ -9536,7 +9428,7 @@
         <v>25</v>
       </c>
       <c r="I147" s="4" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="J147" s="4" t="s">
         <v>27</v>
@@ -9551,7 +9443,7 @@
         <v>4923600</v>
       </c>
       <c r="N147" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O147" s="7">
         <v>1</v>
@@ -9574,13 +9466,13 @@
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D148" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E148" s="4" t="s">
         <v>200</v>
-      </c>
-      <c r="E148" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="F148" s="4" t="s">
         <v>23</v>
@@ -9592,7 +9484,7 @@
         <v>25</v>
       </c>
       <c r="I148" s="4" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="J148" s="4" t="s">
         <v>27</v>
@@ -9607,7 +9499,7 @@
         <v>4923600</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O148" s="7">
         <v>1</v>
@@ -9630,13 +9522,13 @@
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D149" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E149" s="4" t="s">
         <v>200</v>
-      </c>
-      <c r="E149" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="F149" s="4" t="s">
         <v>23</v>
@@ -9648,7 +9540,7 @@
         <v>25</v>
       </c>
       <c r="I149" s="4" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="J149" s="4" t="s">
         <v>27</v>
@@ -9663,7 +9555,7 @@
         <v>4923600</v>
       </c>
       <c r="N149" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O149" s="7">
         <v>1</v>
@@ -9686,13 +9578,13 @@
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="F150" s="4" t="s">
         <v>23</v>
@@ -9704,7 +9596,7 @@
         <v>25</v>
       </c>
       <c r="I150" s="4" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="J150" s="4" t="s">
         <v>27</v>
@@ -9719,7 +9611,7 @@
         <v>1980000</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O150" s="7">
         <v>1</v>
@@ -9742,13 +9634,13 @@
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>23</v>
@@ -9760,7 +9652,7 @@
         <v>25</v>
       </c>
       <c r="I151" s="4" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="J151" s="4" t="s">
         <v>27</v>
@@ -9775,7 +9667,7 @@
         <v>4923600</v>
       </c>
       <c r="N151" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O151" s="7">
         <v>1</v>
@@ -9798,26 +9690,26 @@
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D152" s="3"/>
       <c r="E152" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H152" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I152" s="4" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="J152" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K152" s="6">
         <v>5038</v>
@@ -9852,26 +9744,26 @@
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D153" s="3"/>
       <c r="E153" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I153" s="4" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="J153" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K153" s="6">
         <v>642.99</v>
@@ -9906,26 +9798,26 @@
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D154" s="3"/>
       <c r="E154" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H154" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I154" s="4" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="J154" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K154" s="6">
         <v>642.99</v>
@@ -9960,26 +9852,26 @@
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D155" s="3"/>
       <c r="E155" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H155" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I155" s="4" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="J155" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K155" s="6">
         <v>5.45</v>
@@ -10014,23 +9906,23 @@
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D156" s="3"/>
       <c r="E156" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H156" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I156" s="4" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="J156" s="4" t="s">
         <v>27</v>
@@ -10068,26 +9960,26 @@
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D157" s="3"/>
       <c r="E157" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I157" s="4" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="J157" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K157" s="6">
         <v>3054</v>
@@ -10122,23 +10014,23 @@
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D158" s="3"/>
       <c r="E158" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H158" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I158" s="4" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="J158" s="4" t="s">
         <v>27</v>
@@ -10176,26 +10068,26 @@
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D159" s="3"/>
       <c r="E159" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I159" s="4" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="J159" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K159" s="6">
         <v>280</v>
@@ -10230,26 +10122,26 @@
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D160" s="3"/>
       <c r="E160" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I160" s="4" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="J160" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K160" s="6">
         <v>280</v>
@@ -10284,26 +10176,26 @@
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D161" s="3"/>
       <c r="E161" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H161" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I161" s="4" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="J161" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K161" s="6">
         <v>280</v>
@@ -10338,26 +10230,26 @@
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D162" s="3"/>
       <c r="E162" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H162" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I162" s="4" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="J162" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K162" s="6">
         <v>280</v>
@@ -10392,26 +10284,26 @@
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D163" s="3"/>
       <c r="E163" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H163" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I163" s="4" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="J163" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K163" s="6">
         <v>280</v>
@@ -10446,26 +10338,26 @@
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D164" s="3"/>
       <c r="E164" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I164" s="4" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="J164" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K164" s="6">
         <v>280</v>
@@ -10500,23 +10392,23 @@
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D165" s="3"/>
       <c r="E165" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H165" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I165" s="4" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="J165" s="4" t="s">
         <v>27</v>
@@ -10552,23 +10444,23 @@
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D166" s="3"/>
       <c r="E166" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I166" s="4" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="J166" s="4" t="s">
         <v>27</v>
@@ -10606,23 +10498,23 @@
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D167" s="3"/>
       <c r="E167" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H167" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I167" s="4" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="J167" s="4" t="s">
         <v>27</v>
@@ -10660,26 +10552,26 @@
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D168" s="3"/>
       <c r="E168" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G168" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="H168" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I168" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="F168" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G168" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="H168" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I168" s="4" t="s">
-        <v>262</v>
-      </c>
       <c r="J168" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K168" s="6">
         <v>899.25</v>
@@ -10714,23 +10606,23 @@
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D169" s="3"/>
       <c r="E169" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H169" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I169" s="4" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="J169" s="4" t="s">
         <v>27</v>
@@ -10768,23 +10660,23 @@
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D170" s="3"/>
       <c r="E170" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I170" s="4" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="J170" s="4" t="s">
         <v>27</v>
@@ -10799,7 +10691,7 @@
         <v>100915200</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O170" s="7">
         <v>1</v>
@@ -10822,26 +10714,26 @@
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D171" s="3"/>
       <c r="E171" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H171" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I171" s="4" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="J171" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K171" s="6">
         <v>642.99</v>
@@ -10876,23 +10768,23 @@
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D172" s="3"/>
       <c r="E172" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H172" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I172" s="4" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="J172" s="4" t="s">
         <v>27</v>
@@ -10930,23 +10822,23 @@
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D173" s="3"/>
       <c r="E173" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H173" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I173" s="4" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="J173" s="4" t="s">
         <v>27</v>
@@ -10984,23 +10876,23 @@
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D174" s="3"/>
       <c r="E174" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H174" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I174" s="4" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="J174" s="4" t="s">
         <v>27</v>
@@ -11036,26 +10928,26 @@
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D175" s="3"/>
       <c r="E175" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H175" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I175" s="4" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="J175" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K175" s="6">
         <v>3936</v>
@@ -11090,23 +10982,23 @@
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D176" s="3"/>
       <c r="E176" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H176" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I176" s="4" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="J176" s="4" t="s">
         <v>27</v>
@@ -11144,23 +11036,23 @@
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D177" s="3"/>
       <c r="E177" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H177" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I177" s="4" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="J177" s="4" t="s">
         <v>27</v>
@@ -11198,23 +11090,23 @@
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D178" s="3"/>
       <c r="E178" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H178" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I178" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J178" s="4" t="s">
         <v>27</v>
@@ -11250,23 +11142,23 @@
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D179" s="3"/>
       <c r="E179" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H179" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I179" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J179" s="4" t="s">
         <v>27</v>
@@ -11302,23 +11194,23 @@
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D180" s="3"/>
       <c r="E180" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H180" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I180" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J180" s="4" t="s">
         <v>27</v>
@@ -11354,23 +11246,23 @@
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D181" s="3"/>
       <c r="E181" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H181" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I181" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J181" s="4" t="s">
         <v>27</v>
@@ -11406,23 +11298,23 @@
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D182" s="3"/>
       <c r="E182" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H182" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I182" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J182" s="4" t="s">
         <v>27</v>
@@ -11458,23 +11350,23 @@
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D183" s="3"/>
       <c r="E183" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H183" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I183" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J183" s="4" t="s">
         <v>27</v>
@@ -11510,23 +11402,23 @@
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D184" s="3"/>
       <c r="E184" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H184" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I184" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J184" s="4" t="s">
         <v>27</v>
@@ -11562,23 +11454,23 @@
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D185" s="3"/>
       <c r="E185" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H185" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I185" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J185" s="4" t="s">
         <v>27</v>
@@ -11614,23 +11506,23 @@
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D186" s="3"/>
       <c r="E186" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I186" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J186" s="4" t="s">
         <v>27</v>
@@ -11666,23 +11558,23 @@
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D187" s="3"/>
       <c r="E187" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H187" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I187" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J187" s="4" t="s">
         <v>27</v>
@@ -11718,23 +11610,23 @@
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D188" s="3"/>
       <c r="E188" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H188" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I188" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J188" s="4" t="s">
         <v>27</v>
@@ -11770,23 +11662,23 @@
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D189" s="3"/>
       <c r="E189" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G189" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I189" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J189" s="4" t="s">
         <v>27</v>
@@ -11822,23 +11714,23 @@
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D190" s="3"/>
       <c r="E190" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G190" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H190" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I190" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J190" s="4" t="s">
         <v>27</v>
@@ -11874,23 +11766,23 @@
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D191" s="3"/>
       <c r="E191" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G191" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H191" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I191" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J191" s="4" t="s">
         <v>27</v>
@@ -11926,23 +11818,23 @@
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D192" s="3"/>
       <c r="E192" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G192" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H192" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I192" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J192" s="4" t="s">
         <v>27</v>
@@ -11978,23 +11870,23 @@
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D193" s="3"/>
       <c r="E193" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G193" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H193" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I193" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J193" s="4" t="s">
         <v>27</v>
@@ -12030,23 +11922,23 @@
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D194" s="3"/>
       <c r="E194" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G194" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I194" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J194" s="4" t="s">
         <v>27</v>
@@ -12082,23 +11974,23 @@
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D195" s="3"/>
       <c r="E195" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G195" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H195" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I195" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J195" s="4" t="s">
         <v>27</v>
@@ -12134,23 +12026,23 @@
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D196" s="3"/>
       <c r="E196" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G196" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H196" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I196" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J196" s="4" t="s">
         <v>27</v>
@@ -12186,23 +12078,23 @@
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D197" s="3"/>
       <c r="E197" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G197" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H197" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I197" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J197" s="4" t="s">
         <v>27</v>
@@ -12238,23 +12130,23 @@
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D198" s="3"/>
       <c r="E198" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G198" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H198" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I198" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J198" s="4" t="s">
         <v>27</v>
@@ -12292,23 +12184,23 @@
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D199" s="3"/>
       <c r="E199" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G199" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H199" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I199" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J199" s="4" t="s">
         <v>27</v>
@@ -12346,23 +12238,23 @@
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D200" s="3"/>
       <c r="E200" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G200" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H200" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I200" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J200" s="4" t="s">
         <v>27</v>
@@ -12400,23 +12292,23 @@
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D201" s="3"/>
       <c r="E201" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G201" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H201" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I201" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J201" s="4" t="s">
         <v>27</v>
@@ -12454,23 +12346,23 @@
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D202" s="3"/>
       <c r="E202" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G202" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H202" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I202" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J202" s="4" t="s">
         <v>27</v>
@@ -12508,23 +12400,23 @@
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D203" s="3"/>
       <c r="E203" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G203" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H203" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I203" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J203" s="4" t="s">
         <v>27</v>
@@ -12562,23 +12454,23 @@
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D204" s="3"/>
       <c r="E204" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G204" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H204" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I204" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J204" s="4" t="s">
         <v>27</v>
@@ -12616,26 +12508,26 @@
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D205" s="3"/>
       <c r="E205" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G205" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H205" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I205" s="4" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="J205" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K205" s="6">
         <v>2465</v>
@@ -12670,26 +12562,26 @@
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D206" s="3"/>
       <c r="E206" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G206" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H206" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I206" s="4" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="J206" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K206" s="6">
         <v>2465</v>
@@ -12724,26 +12616,26 @@
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D207" s="3"/>
       <c r="E207" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G207" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H207" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I207" s="4" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="J207" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K207" s="6">
         <v>2465</v>
@@ -12778,26 +12670,26 @@
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
       <c r="C208" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D208" s="3"/>
       <c r="E208" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G208" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I208" s="4" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="J208" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K208" s="6">
         <v>2465</v>
@@ -12832,26 +12724,26 @@
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D209" s="3"/>
       <c r="E209" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G209" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I209" s="4" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="J209" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K209" s="6">
         <v>2465</v>
@@ -12886,26 +12778,26 @@
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D210" s="3"/>
       <c r="E210" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G210" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I210" s="4" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="J210" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K210" s="6">
         <v>2465</v>
@@ -12940,23 +12832,23 @@
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D211" s="3"/>
       <c r="E211" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G211" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I211" s="4" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="J211" s="4" t="s">
         <v>27</v>
@@ -12971,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="N211" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O211" s="7" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="P211" s="6">
         <v>0</v>
@@ -12994,23 +12886,23 @@
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D212" s="3"/>
       <c r="E212" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G212" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I212" s="4" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="J212" s="4" t="s">
         <v>27</v>
@@ -13025,10 +12917,10 @@
         <v>0</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O212" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="P212" s="6">
         <v>0</v>
@@ -13048,23 +12940,23 @@
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D213" s="3"/>
       <c r="E213" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G213" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H213" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I213" s="4" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="J213" s="4" t="s">
         <v>27</v>
@@ -13079,10 +12971,10 @@
         <v>0</v>
       </c>
       <c r="N213" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O213" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="P213" s="6">
         <v>0</v>
@@ -13102,23 +12994,23 @@
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D214" s="3"/>
       <c r="E214" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G214" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H214" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I214" s="4" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="J214" s="4" t="s">
         <v>27</v>
@@ -13133,10 +13025,10 @@
         <v>0</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O214" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="P214" s="6">
         <v>0</v>
@@ -13156,23 +13048,23 @@
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D215" s="3"/>
       <c r="E215" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G215" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H215" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I215" s="4" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="J215" s="4" t="s">
         <v>27</v>
@@ -13187,10 +13079,10 @@
         <v>0</v>
       </c>
       <c r="N215" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O215" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="P215" s="6">
         <v>0</v>
@@ -13210,23 +13102,23 @@
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D216" s="3"/>
       <c r="E216" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G216" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H216" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I216" s="4" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J216" s="4" t="s">
         <v>27</v>
@@ -13239,7 +13131,7 @@
         <v>56191200</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O216" s="4"/>
       <c r="P216" s="6"/>
@@ -13252,26 +13144,26 @@
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D217" s="3"/>
       <c r="E217" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G217" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H217" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I217" s="4" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="J217" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K217" s="6">
         <v>141.81</v>
@@ -13283,7 +13175,7 @@
         <v>2478521.1456</v>
       </c>
       <c r="N217" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O217" s="4"/>
       <c r="P217" s="6"/>
@@ -13296,26 +13188,26 @@
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D218" s="3"/>
       <c r="E218" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G218" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H218" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I218" s="4" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="J218" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K218" s="6">
         <v>141.81</v>
@@ -13327,7 +13219,7 @@
         <v>2478521.1456</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O218" s="4"/>
       <c r="P218" s="3"/>
@@ -13340,26 +13232,26 @@
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D219" s="3"/>
       <c r="E219" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G219" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H219" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I219" s="4" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="J219" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K219" s="6">
         <v>141.81</v>
@@ -13371,7 +13263,7 @@
         <v>2478521.1456</v>
       </c>
       <c r="N219" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O219" s="4"/>
       <c r="P219" s="3"/>
@@ -13384,26 +13276,26 @@
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D220" s="3"/>
       <c r="E220" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G220" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H220" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I220" s="4" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="J220" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K220" s="6">
         <v>141.81</v>
@@ -13415,7 +13307,7 @@
         <v>2478521.1456</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O220" s="4"/>
       <c r="P220" s="3"/>
@@ -13428,26 +13320,26 @@
       <c r="A221" s="3"/>
       <c r="B221" s="3"/>
       <c r="C221" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D221" s="3"/>
       <c r="E221" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G221" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H221" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I221" s="4" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="J221" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K221" s="6">
         <v>141.81</v>
@@ -13459,7 +13351,7 @@
         <v>2478521.1456</v>
       </c>
       <c r="N221" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O221" s="4"/>
       <c r="P221" s="3"/>
@@ -13472,23 +13364,23 @@
       <c r="A222" s="3"/>
       <c r="B222" s="3"/>
       <c r="C222" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D222" s="3"/>
       <c r="E222" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G222" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I222" s="4" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="J222" s="4" t="s">
         <v>27</v>
@@ -13503,7 +13395,7 @@
         <v>2478521.1456</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O222" s="4"/>
       <c r="P222" s="3"/>
@@ -13516,23 +13408,23 @@
       <c r="A223" s="3"/>
       <c r="B223" s="3"/>
       <c r="C223" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D223" s="3"/>
       <c r="E223" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G223" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H223" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I223" s="4" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="J223" s="4" t="s">
         <v>27</v>
@@ -13545,7 +13437,7 @@
         <v>94554000</v>
       </c>
       <c r="N223" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O223" s="4"/>
       <c r="P223" s="3"/>
@@ -13558,23 +13450,23 @@
       <c r="A224" s="3"/>
       <c r="B224" s="3"/>
       <c r="C224" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D224" s="3"/>
       <c r="E224" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G224" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H224" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I224" s="4" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="J224" s="4" t="s">
         <v>27</v>
@@ -13587,7 +13479,7 @@
         <v>94554000</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O224" s="4"/>
       <c r="P224" s="3"/>
@@ -13600,23 +13492,23 @@
       <c r="A225" s="3"/>
       <c r="B225" s="3"/>
       <c r="C225" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D225" s="3"/>
       <c r="E225" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G225" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H225" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I225" s="4" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="J225" s="4" t="s">
         <v>27</v>
@@ -13629,7 +13521,7 @@
         <v>32276400</v>
       </c>
       <c r="N225" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O225" s="4"/>
       <c r="P225" s="3"/>
@@ -13642,26 +13534,26 @@
       <c r="A226" s="3"/>
       <c r="B226" s="3"/>
       <c r="C226" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D226" s="3"/>
       <c r="E226" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G226" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H226" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I226" s="4" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="J226" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K226" s="6"/>
       <c r="L226" s="6">
@@ -13671,7 +13563,7 @@
         <v>32276400</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O226" s="4"/>
       <c r="P226" s="3"/>
@@ -13684,26 +13576,26 @@
       <c r="A227" s="3"/>
       <c r="B227" s="3"/>
       <c r="C227" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D227" s="3"/>
       <c r="E227" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G227" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H227" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I227" s="4" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="J227" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K227" s="6">
         <v>1611</v>
@@ -13715,7 +13607,7 @@
         <v>28156671.360000003</v>
       </c>
       <c r="N227" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O227" s="4"/>
       <c r="P227" s="3"/>
@@ -13728,26 +13620,26 @@
       <c r="A228" s="3"/>
       <c r="B228" s="3"/>
       <c r="C228" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D228" s="3"/>
       <c r="E228" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G228" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H228" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I228" s="4" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="J228" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K228" s="6">
         <v>3012</v>
@@ -13759,7 +13651,7 @@
         <v>52643013.12</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O228" s="4"/>
       <c r="P228" s="3"/>
@@ -13772,26 +13664,26 @@
       <c r="A229" s="3"/>
       <c r="B229" s="3"/>
       <c r="C229" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D229" s="3"/>
       <c r="E229" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G229" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H229" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I229" s="4" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="J229" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K229" s="6">
         <v>7856</v>
@@ -13803,7 +13695,7 @@
         <v>137305282.56</v>
       </c>
       <c r="N229" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O229" s="4"/>
       <c r="P229" s="3"/>
@@ -13816,23 +13708,23 @@
       <c r="A230" s="3"/>
       <c r="B230" s="3"/>
       <c r="C230" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D230" s="3"/>
       <c r="E230" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G230" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H230" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I230" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J230" s="4" t="s">
         <v>27</v>
@@ -13845,7 +13737,7 @@
         <v>4448400</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O230" s="4"/>
       <c r="P230" s="3"/>
@@ -13858,23 +13750,23 @@
       <c r="A231" s="3"/>
       <c r="B231" s="3"/>
       <c r="C231" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D231" s="3"/>
       <c r="E231" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G231" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H231" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I231" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J231" s="4" t="s">
         <v>27</v>
@@ -13887,7 +13779,7 @@
         <v>4448400</v>
       </c>
       <c r="N231" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O231" s="4"/>
       <c r="P231" s="3"/>
@@ -13900,23 +13792,23 @@
       <c r="A232" s="3"/>
       <c r="B232" s="3"/>
       <c r="C232" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D232" s="3"/>
       <c r="E232" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G232" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H232" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I232" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J232" s="4" t="s">
         <v>27</v>
@@ -13929,7 +13821,7 @@
         <v>4448400</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O232" s="4"/>
       <c r="P232" s="3"/>
@@ -13942,23 +13834,23 @@
       <c r="A233" s="3"/>
       <c r="B233" s="3"/>
       <c r="C233" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D233" s="3"/>
       <c r="E233" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G233" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H233" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I233" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J233" s="4" t="s">
         <v>27</v>
@@ -13971,7 +13863,7 @@
         <v>4448400</v>
       </c>
       <c r="N233" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O233" s="4"/>
       <c r="P233" s="3"/>
@@ -13984,23 +13876,23 @@
       <c r="A234" s="3"/>
       <c r="B234" s="3"/>
       <c r="C234" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D234" s="3"/>
       <c r="E234" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G234" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H234" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I234" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J234" s="4" t="s">
         <v>27</v>
@@ -14013,7 +13905,7 @@
         <v>4448400</v>
       </c>
       <c r="N234" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O234" s="4"/>
       <c r="P234" s="3"/>
@@ -14026,23 +13918,23 @@
       <c r="A235" s="3"/>
       <c r="B235" s="3"/>
       <c r="C235" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D235" s="3"/>
       <c r="E235" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G235" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H235" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I235" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J235" s="4" t="s">
         <v>27</v>
@@ -14055,7 +13947,7 @@
         <v>4448400</v>
       </c>
       <c r="N235" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O235" s="4"/>
       <c r="P235" s="3"/>
@@ -14068,23 +13960,23 @@
       <c r="A236" s="3"/>
       <c r="B236" s="3"/>
       <c r="C236" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D236" s="3"/>
       <c r="E236" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G236" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H236" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I236" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J236" s="4" t="s">
         <v>27</v>
@@ -14097,7 +13989,7 @@
         <v>4448400</v>
       </c>
       <c r="N236" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O236" s="4"/>
       <c r="P236" s="3"/>
@@ -14110,23 +14002,23 @@
       <c r="A237" s="3"/>
       <c r="B237" s="3"/>
       <c r="C237" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D237" s="3"/>
       <c r="E237" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G237" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H237" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I237" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J237" s="4" t="s">
         <v>27</v>
@@ -14139,7 +14031,7 @@
         <v>4448400</v>
       </c>
       <c r="N237" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O237" s="4"/>
       <c r="P237" s="3"/>
@@ -14152,23 +14044,23 @@
       <c r="A238" s="3"/>
       <c r="B238" s="3"/>
       <c r="C238" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D238" s="3"/>
       <c r="E238" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G238" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I238" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J238" s="4" t="s">
         <v>27</v>
@@ -14181,7 +14073,7 @@
         <v>4448400</v>
       </c>
       <c r="N238" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O238" s="4"/>
       <c r="P238" s="3"/>
@@ -14194,23 +14086,23 @@
       <c r="A239" s="3"/>
       <c r="B239" s="3"/>
       <c r="C239" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D239" s="3"/>
       <c r="E239" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G239" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H239" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I239" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J239" s="4" t="s">
         <v>27</v>
@@ -14223,7 +14115,7 @@
         <v>4448400</v>
       </c>
       <c r="N239" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O239" s="4"/>
       <c r="P239" s="3"/>
@@ -14236,23 +14128,23 @@
       <c r="A240" s="3"/>
       <c r="B240" s="3"/>
       <c r="C240" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D240" s="3"/>
       <c r="E240" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G240" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H240" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I240" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J240" s="4" t="s">
         <v>27</v>
@@ -14265,7 +14157,7 @@
         <v>4448400</v>
       </c>
       <c r="N240" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O240" s="4"/>
       <c r="P240" s="3"/>
@@ -14278,23 +14170,23 @@
       <c r="A241" s="3"/>
       <c r="B241" s="3"/>
       <c r="C241" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D241" s="3"/>
       <c r="E241" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G241" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H241" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I241" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J241" s="4" t="s">
         <v>27</v>
@@ -14307,7 +14199,7 @@
         <v>4448400</v>
       </c>
       <c r="N241" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O241" s="4"/>
       <c r="P241" s="3"/>
@@ -14320,23 +14212,23 @@
       <c r="A242" s="3"/>
       <c r="B242" s="3"/>
       <c r="C242" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D242" s="3"/>
       <c r="E242" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G242" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H242" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I242" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J242" s="4" t="s">
         <v>27</v>
@@ -14349,7 +14241,7 @@
         <v>4448400</v>
       </c>
       <c r="N242" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O242" s="4"/>
       <c r="P242" s="3"/>
@@ -14362,23 +14254,23 @@
       <c r="A243" s="3"/>
       <c r="B243" s="3"/>
       <c r="C243" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D243" s="3"/>
       <c r="E243" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G243" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H243" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I243" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J243" s="4" t="s">
         <v>27</v>
@@ -14391,7 +14283,7 @@
         <v>4448400</v>
       </c>
       <c r="N243" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O243" s="4"/>
       <c r="P243" s="3"/>
@@ -14404,23 +14296,23 @@
       <c r="A244" s="3"/>
       <c r="B244" s="3"/>
       <c r="C244" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D244" s="3"/>
       <c r="E244" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G244" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H244" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I244" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J244" s="4" t="s">
         <v>27</v>
@@ -14433,7 +14325,7 @@
         <v>4448400</v>
       </c>
       <c r="N244" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O244" s="4"/>
       <c r="P244" s="3"/>
@@ -14446,23 +14338,23 @@
       <c r="A245" s="3"/>
       <c r="B245" s="3"/>
       <c r="C245" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D245" s="3"/>
       <c r="E245" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G245" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H245" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I245" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J245" s="4" t="s">
         <v>27</v>
@@ -14475,7 +14367,7 @@
         <v>4448400</v>
       </c>
       <c r="N245" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O245" s="4"/>
       <c r="P245" s="3"/>
@@ -14488,23 +14380,23 @@
       <c r="A246" s="3"/>
       <c r="B246" s="3"/>
       <c r="C246" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D246" s="3"/>
       <c r="E246" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G246" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H246" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I246" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J246" s="4" t="s">
         <v>27</v>
@@ -14517,7 +14409,7 @@
         <v>4448400</v>
       </c>
       <c r="N246" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O246" s="4"/>
       <c r="P246" s="3"/>
@@ -14530,23 +14422,23 @@
       <c r="A247" s="3"/>
       <c r="B247" s="3"/>
       <c r="C247" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D247" s="3"/>
       <c r="E247" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G247" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H247" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I247" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J247" s="4" t="s">
         <v>27</v>
@@ -14559,7 +14451,7 @@
         <v>4448400</v>
       </c>
       <c r="N247" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O247" s="4"/>
       <c r="P247" s="3"/>
@@ -14572,23 +14464,23 @@
       <c r="A248" s="3"/>
       <c r="B248" s="3"/>
       <c r="C248" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D248" s="3"/>
       <c r="E248" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G248" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H248" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I248" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J248" s="4" t="s">
         <v>27</v>
@@ -14601,7 +14493,7 @@
         <v>4448400</v>
       </c>
       <c r="N248" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O248" s="4"/>
       <c r="P248" s="3"/>
@@ -14614,23 +14506,23 @@
       <c r="A249" s="3"/>
       <c r="B249" s="3"/>
       <c r="C249" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D249" s="3"/>
       <c r="E249" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G249" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H249" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I249" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J249" s="4" t="s">
         <v>27</v>
@@ -14643,7 +14535,7 @@
         <v>4448400</v>
       </c>
       <c r="N249" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O249" s="4"/>
       <c r="P249" s="3"/>
@@ -14656,23 +14548,23 @@
       <c r="A250" s="3"/>
       <c r="B250" s="3"/>
       <c r="C250" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D250" s="3"/>
       <c r="E250" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G250" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H250" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I250" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J250" s="4" t="s">
         <v>27</v>
@@ -14685,7 +14577,7 @@
         <v>4448400</v>
       </c>
       <c r="N250" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O250" s="4"/>
       <c r="P250" s="3"/>
@@ -14698,23 +14590,23 @@
       <c r="A251" s="3"/>
       <c r="B251" s="3"/>
       <c r="C251" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D251" s="3"/>
       <c r="E251" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G251" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H251" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I251" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J251" s="4" t="s">
         <v>27</v>
@@ -14727,7 +14619,7 @@
         <v>4448400</v>
       </c>
       <c r="N251" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O251" s="4"/>
       <c r="P251" s="3"/>
@@ -14740,23 +14632,23 @@
       <c r="A252" s="3"/>
       <c r="B252" s="3"/>
       <c r="C252" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D252" s="3"/>
       <c r="E252" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G252" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H252" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I252" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J252" s="4" t="s">
         <v>27</v>
@@ -14769,7 +14661,7 @@
         <v>4448400</v>
       </c>
       <c r="N252" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O252" s="4"/>
       <c r="P252" s="3"/>
@@ -14782,23 +14674,23 @@
       <c r="A253" s="3"/>
       <c r="B253" s="3"/>
       <c r="C253" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D253" s="3"/>
       <c r="E253" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G253" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H253" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I253" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J253" s="4" t="s">
         <v>27</v>
@@ -14811,7 +14703,7 @@
         <v>4448400</v>
       </c>
       <c r="N253" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O253" s="4"/>
       <c r="P253" s="3"/>
@@ -14824,23 +14716,23 @@
       <c r="A254" s="3"/>
       <c r="B254" s="3"/>
       <c r="C254" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D254" s="3"/>
       <c r="E254" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G254" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H254" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I254" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J254" s="4" t="s">
         <v>27</v>
@@ -14853,7 +14745,7 @@
         <v>4448400</v>
       </c>
       <c r="N254" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O254" s="4"/>
       <c r="P254" s="3"/>
@@ -14866,23 +14758,23 @@
       <c r="A255" s="3"/>
       <c r="B255" s="3"/>
       <c r="C255" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D255" s="3"/>
       <c r="E255" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G255" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H255" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I255" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J255" s="4" t="s">
         <v>27</v>
@@ -14895,7 +14787,7 @@
         <v>4448400</v>
       </c>
       <c r="N255" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O255" s="4"/>
       <c r="P255" s="3"/>
@@ -14908,23 +14800,23 @@
       <c r="A256" s="3"/>
       <c r="B256" s="3"/>
       <c r="C256" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D256" s="3"/>
       <c r="E256" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G256" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H256" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I256" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J256" s="4" t="s">
         <v>27</v>
@@ -14937,7 +14829,7 @@
         <v>4448400</v>
       </c>
       <c r="N256" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O256" s="4"/>
       <c r="P256" s="3"/>
@@ -14950,23 +14842,23 @@
       <c r="A257" s="3"/>
       <c r="B257" s="3"/>
       <c r="C257" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D257" s="3"/>
       <c r="E257" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G257" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H257" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I257" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J257" s="4" t="s">
         <v>27</v>
@@ -14979,7 +14871,7 @@
         <v>4448400</v>
       </c>
       <c r="N257" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O257" s="4"/>
       <c r="P257" s="3"/>
@@ -14992,23 +14884,23 @@
       <c r="A258" s="3"/>
       <c r="B258" s="3"/>
       <c r="C258" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D258" s="3"/>
       <c r="E258" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G258" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H258" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I258" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J258" s="4" t="s">
         <v>27</v>
@@ -15021,7 +14913,7 @@
         <v>4448400</v>
       </c>
       <c r="N258" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O258" s="4"/>
       <c r="P258" s="3"/>
@@ -15034,23 +14926,23 @@
       <c r="A259" s="3"/>
       <c r="B259" s="3"/>
       <c r="C259" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D259" s="3"/>
       <c r="E259" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G259" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H259" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I259" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J259" s="4" t="s">
         <v>27</v>
@@ -15063,7 +14955,7 @@
         <v>4448400</v>
       </c>
       <c r="N259" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O259" s="4"/>
       <c r="P259" s="3"/>
@@ -15076,23 +14968,23 @@
       <c r="A260" s="3"/>
       <c r="B260" s="3"/>
       <c r="C260" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D260" s="3"/>
       <c r="E260" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G260" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H260" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I260" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J260" s="4" t="s">
         <v>27</v>
@@ -15105,7 +14997,7 @@
         <v>4448400</v>
       </c>
       <c r="N260" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O260" s="4"/>
       <c r="P260" s="3"/>
@@ -15118,23 +15010,23 @@
       <c r="A261" s="3"/>
       <c r="B261" s="3"/>
       <c r="C261" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D261" s="3"/>
       <c r="E261" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G261" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H261" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I261" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J261" s="4" t="s">
         <v>27</v>
@@ -15147,7 +15039,7 @@
         <v>4448400</v>
       </c>
       <c r="N261" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O261" s="4"/>
       <c r="P261" s="3"/>
@@ -15160,23 +15052,23 @@
       <c r="A262" s="3"/>
       <c r="B262" s="3"/>
       <c r="C262" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D262" s="3"/>
       <c r="E262" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F262" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G262" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H262" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I262" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J262" s="4" t="s">
         <v>27</v>
@@ -15189,7 +15081,7 @@
         <v>4448400</v>
       </c>
       <c r="N262" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O262" s="4"/>
       <c r="P262" s="3"/>
@@ -15202,23 +15094,23 @@
       <c r="A263" s="3"/>
       <c r="B263" s="3"/>
       <c r="C263" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D263" s="3"/>
       <c r="E263" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G263" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H263" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I263" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J263" s="4" t="s">
         <v>27</v>
@@ -15231,7 +15123,7 @@
         <v>4448400</v>
       </c>
       <c r="N263" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O263" s="4"/>
       <c r="P263" s="3"/>
@@ -15244,23 +15136,23 @@
       <c r="A264" s="3"/>
       <c r="B264" s="3"/>
       <c r="C264" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D264" s="3"/>
       <c r="E264" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G264" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H264" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I264" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J264" s="4" t="s">
         <v>27</v>
@@ -15273,7 +15165,7 @@
         <v>4448400</v>
       </c>
       <c r="N264" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O264" s="4"/>
       <c r="P264" s="3"/>
@@ -15286,23 +15178,23 @@
       <c r="A265" s="3"/>
       <c r="B265" s="3"/>
       <c r="C265" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D265" s="3"/>
       <c r="E265" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F265" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G265" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H265" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I265" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J265" s="4" t="s">
         <v>27</v>
@@ -15315,7 +15207,7 @@
         <v>4448400</v>
       </c>
       <c r="N265" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O265" s="4"/>
       <c r="P265" s="3"/>
@@ -15328,23 +15220,23 @@
       <c r="A266" s="3"/>
       <c r="B266" s="3"/>
       <c r="C266" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D266" s="3"/>
       <c r="E266" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F266" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G266" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H266" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I266" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J266" s="4" t="s">
         <v>27</v>
@@ -15357,7 +15249,7 @@
         <v>4448400</v>
       </c>
       <c r="N266" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O266" s="4"/>
       <c r="P266" s="3"/>
@@ -15370,23 +15262,23 @@
       <c r="A267" s="3"/>
       <c r="B267" s="3"/>
       <c r="C267" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D267" s="3"/>
       <c r="E267" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F267" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G267" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H267" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I267" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J267" s="4" t="s">
         <v>27</v>
@@ -15399,7 +15291,7 @@
         <v>4448400</v>
       </c>
       <c r="N267" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O267" s="4"/>
       <c r="P267" s="3"/>
@@ -15412,23 +15304,23 @@
       <c r="A268" s="3"/>
       <c r="B268" s="3"/>
       <c r="C268" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D268" s="3"/>
       <c r="E268" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F268" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G268" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H268" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I268" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J268" s="4" t="s">
         <v>27</v>
@@ -15441,7 +15333,7 @@
         <v>4448400</v>
       </c>
       <c r="N268" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O268" s="4"/>
       <c r="P268" s="3"/>
@@ -15478,7 +15370,7 @@
     <mergeCell ref="S67:S68"/>
     <mergeCell ref="T67:T68"/>
   </mergeCells>
-  <dataValidations count="31">
+  <dataValidations count="24">
     <dataValidation type="list" allowBlank="1" sqref="C126:C145">
       <formula1>"유지(단가변동), 유지(단가동일), 해지, 신규"</formula1>
     </dataValidation>
@@ -15509,12 +15401,6 @@
     <dataValidation type="list" allowBlank="1" sqref="E110:E119">
       <formula1>"유지(단가변동), 유지(단가동일), 해지, 신규"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G10:G57">
-      <formula1>"별도단말,Web접속,API연계,기타"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G100:G268">
-      <formula1>"별도단말,Web접속,API연계,기타"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="G3:G57">
       <formula1>"별도단말,Web접속,API연계,기타"</formula1>
     </dataValidation>
@@ -15526,12 +15412,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="G69:G268">
       <formula1>"별도단말,Web접속,API연계,기타"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H10:H57">
-      <formula1>"리서치,트레이딩,리스크관리,기타"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H100:H268">
-      <formula1>"리서치,트레이딩,리스크관리,기타"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="H3:H57">
       <formula1>"리서치,트레이딩,리스크관리,기타"</formula1>
@@ -15554,17 +15434,8 @@
     <dataValidation type="list" allowBlank="1" sqref="J3:J268">
       <formula1>"KRW,USD,EUR,JPY,GBP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N10:N268">
-      <formula1>"유지(단가변동), 유지(단가동일), 해지, 신규"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="N3:N268">
       <formula1>"유지(단가변동), 유지(단가동일), 해지, 신규"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="S10:S67">
-      <formula1>"월간,분기별,반기별,연간"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="S100:S215">
-      <formula1>"월간,분기별,반기별,연간"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="S3:S67">
       <formula1>"월간,분기별,반기별,연간"</formula1>
